--- a/data/base/Backlog_47.xlsx
+++ b/data/base/Backlog_47.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5775DBC-5D12-46BE-A3CB-F4E0AD08E725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EBFD3EC-9618-4825-B020-4E5A56FC8C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="37">
   <si>
     <t>Setor</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>Maria de Oliveira</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
         <v>45985</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>13</v>
@@ -755,7 +758,7 @@
         <v>45985</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>13</v>
@@ -790,7 +793,7 @@
         <v>45985</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>13</v>
@@ -825,7 +828,7 @@
         <v>45985</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>13</v>
@@ -860,7 +863,7 @@
         <v>45985</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>13</v>
@@ -895,7 +898,7 @@
         <v>45985</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>13</v>
@@ -965,7 +968,7 @@
         <v>45985</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>13</v>
@@ -1105,7 +1108,7 @@
         <v>45985</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>13</v>
@@ -1245,7 +1248,7 @@
         <v>45985</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>13</v>
@@ -1315,7 +1318,7 @@
         <v>45985</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>13</v>
@@ -1350,7 +1353,7 @@
         <v>45985</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>13</v>
@@ -1385,7 +1388,7 @@
         <v>45985</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>13</v>
@@ -1420,7 +1423,7 @@
         <v>45985</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>13</v>
@@ -1455,7 +1458,7 @@
         <v>45985</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>13</v>
@@ -1490,7 +1493,7 @@
         <v>45985</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>13</v>
@@ -1525,7 +1528,7 @@
         <v>45985</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>13</v>
@@ -1560,7 +1563,7 @@
         <v>45985</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>13</v>
@@ -1595,7 +1598,7 @@
         <v>45985</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>13</v>
@@ -1630,7 +1633,7 @@
         <v>45985</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>13</v>
@@ -1665,7 +1668,7 @@
         <v>45985</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>13</v>
@@ -1700,7 +1703,7 @@
         <v>45985</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>13</v>
@@ -1735,7 +1738,7 @@
         <v>45985</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>13</v>
@@ -1770,7 +1773,7 @@
         <v>45985</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>13</v>
@@ -1805,7 +1808,7 @@
         <v>45985</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>13</v>
@@ -1840,7 +1843,7 @@
         <v>45985</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>13</v>
@@ -1875,7 +1878,7 @@
         <v>45985</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>13</v>
@@ -1910,7 +1913,7 @@
         <v>45985</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>13</v>
@@ -1945,7 +1948,7 @@
         <v>45985</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>13</v>
@@ -1980,7 +1983,7 @@
         <v>45985</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>13</v>
@@ -2015,7 +2018,7 @@
         <v>45985</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>13</v>
@@ -2050,7 +2053,7 @@
         <v>45985</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>13</v>
@@ -2260,7 +2263,7 @@
         <v>45985</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>13</v>
@@ -2295,7 +2298,7 @@
         <v>45985</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>13</v>
@@ -2330,7 +2333,7 @@
         <v>45985</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>13</v>
@@ -2400,7 +2403,7 @@
         <v>45985</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>13</v>
@@ -2435,7 +2438,7 @@
         <v>45985</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>13</v>
@@ -2470,7 +2473,7 @@
         <v>45985</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>13</v>
@@ -2505,7 +2508,7 @@
         <v>45985</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>13</v>
@@ -2610,7 +2613,7 @@
         <v>45985</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>13</v>
@@ -2715,7 +2718,7 @@
         <v>45985</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K60" s="9" t="s">
         <v>13</v>
@@ -2955,7 +2958,7 @@
         <v>45985</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>16</v>
@@ -3060,7 +3063,7 @@
         <v>45985</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>16</v>
